--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19839da34dfc3fcb</t>
+          <t>990f0f85adb810f3</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>990f0f85adb810f3</t>
+          <t>a046450d1b60700b</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -115,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -158,11 +158,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="5"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="6"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="7"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -183,6 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="6"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="7"/>
     </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -845,7 +851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1057,33 +1063,29 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>감가상각 실적</t>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>dep_actual</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>억원</t>
-        </is>
-      </c>
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="9" t="n">
-        <v>45007.01</v>
+        <v>1</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>45574.57</v>
+        <v>1</v>
       </c>
       <c r="F6" s="9" t="n">
-        <v>42137.42</v>
+        <v>1</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>51256.37</v>
+        <v>1</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>43541.45</v>
+        <v>1</v>
       </c>
       <c r="I6" s="10" t="n">
         <v>0</v>
@@ -1102,71 +1104,71 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>[객관] 비용의 성격별 분류 주석.</t>
+          <t>[객관] 실적 연도 표시(1). 순이익은 적자 연도가 있어 "실적 &gt; 0" 관용구를 쓸 수 없다 — LGD·삼성전자 DS에서 확립한 hist 마스크 패턴.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>감가상각 증가율</t>
+          <t>순이익 실적</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>dep_g</t>
+          <t>ni_actual</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="13" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J7" s="13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="K7" s="13" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L7" s="13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>-0.03</v>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>11861.82</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>-30715.65</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>-27337.42</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>-25626.06</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>2263.12</v>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="N7" s="11" t="inlineStr">
         <is>
-          <t>[주관] CAPEX가 5.08조(2022) → 1.35조(2025)로 **4년간 73% 줄었다**. 감가상각 4.35조 대비 CAPEX 1.35조 — 신규 투자가 상각 소멸분을 채우지 못하므로 감가상각은 구조적으로 감소한다. 연 −12%에서 −3%로 체감. 이 감소가 영업이익 개선의 기계적 동력이다 (삼성전기의 역방향).</t>
+          <t>[객관] 연결 지배주주 순이익 확정값 (사업보고서 연결포괄손익계산서).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>기타비용 실적</t>
+          <t>영업외손익</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>other_actual</t>
+          <t>nonop</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1175,50 +1177,50 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>231467.34</v>
+        <v>-5117.23</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>236793.71</v>
+        <v>-13483.23</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>196272.41</v>
+        <v>-8292.77</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>220503.06</v>
+        <v>-16309.44</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>209389.6</v>
+        <v>-152.88</v>
       </c>
       <c r="I8" s="10" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>[객관] 확정값에서 역산. 세 항목 모두 공시값이라 결과도 확정이다.</t>
+          <t>[주관 추정 · 실적은 공시값] 영업외손익 = 세전이익 − 영업이익. 실적 −5,117/−13,483/−8,293/−16,309/−153억 — 손상차손이 지배해 과거는 예측 불가. 2025(−153억)를 바닥으로 이자 부담을 감안해 **−300억 고정**. 손상 재발은 Bear의 영역.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>기타비용률</t>
+          <t>실효세율</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>other_ratio</t>
+          <t>tax_rate</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1242,177 +1244,593 @@
         <v>0</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>0.806</v>
+        <v>0.25</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>0.805</v>
+        <v>0.25</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>0.804</v>
+        <v>0.25</v>
       </c>
       <c r="N9" s="11" t="inlineStr">
         <is>
-          <t>[주관] 실적 77.5 → 90.5 → 92.0 → 82.8 → 81.1%. 판가 사이클에 따라 15%p 진동한다. 2025년 수준(81.1%)에서 사실상 고정하고 연 0.1~0.2%p만 개선 — OLED 믹스 개선과 중국 LCD 판가 압박이 상쇄된다고 봤다. 2021년(77.5%) 복귀는 Bull에서만 가정한다.</t>
+          <t>[주관] 실효세율. 2025 실효 39.4%는 이연법인세 영향 — 정상화 25% 가정.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>매출 실적</t>
+          <t>지배지분 비율</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>rev_actual</t>
+          <t>ctrl_ratio</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>억원</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>298780.43</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>261517.81</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>213308.19</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>266153.47</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>258100.82</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>0</v>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L10" s="13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.75</v>
       </c>
       <c r="N10" s="11" t="inlineStr">
         <is>
-          <t>[객관] 요약연결재무정보.</t>
+          <t>[주관] 지배지분 비율. 2025 지배 74.5%(광저우 등 비지배 흑자) — **회복 이익의 1/4은 주주 몫이 아니다**. 75% 고정.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>매출 성장률</t>
+          <t>상장주식수</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>rev_g</t>
+          <t>shares</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>0.01</v>
+          <t>백만주</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>500</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>500</v>
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>[주관] 2026년 −1% 후 연 +1%. 컨센서스 2026 EBITDA가 2025년과 사실상 같은 수준(48,059 vs 48,711억)이라 시장도 매출 성장을 보지 않는다. LCD 축소가 이어지고 OLED(Auto·IT)가 그 공백을 겨우 메우는 그림. 성장이 아니라 **수익성과 레버리지**가 이 종목의 이야기다.</t>
+          <t>[객관] 상장주식수 5.0억주(2024 유상증자 반영) 고정.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
+          <t>DPS 실적</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>dps_a</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>650</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 주당 현금배당. 2021 650원 이후 무배당.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 배당성향 0% — 순차입금 상환이 우선이라 **배당 재개를 가정하지 않는다**. 재개 시나리오는 이 슬라이더로 본다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>감가상각 실적</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>45007.01</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>45574.57</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>42137.42</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>51256.37</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>43541.45</v>
+      </c>
+      <c r="I14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 비용의 성격별 분류 주석.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>[주관] CAPEX가 5.08조(2022) → 1.35조(2025)로 **4년간 73% 줄었다**. 감가상각 4.35조 대비 CAPEX 1.35조 — 신규 투자가 상각 소멸분을 채우지 못하므로 감가상각은 구조적으로 감소한다. 연 −12%에서 −3%로 체감. 이 감소가 영업이익 개선의 기계적 동력이다 (삼성전기의 역방향).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>기타비용 실적</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>other_actual</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>231467.34</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>236793.71</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>196272.41</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>220503.06</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>209389.6</v>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 확정값에서 역산. 세 항목 모두 공시값이라 결과도 확정이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>기타비용률</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>other_ratio</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>0.8080000000000001</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="N17" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 실적 77.5 → 90.5 → 92.0 → 82.8 → 81.1%. 판가 사이클에 따라 15%p 진동한다. 2025년 수준(81.1%)에서 사실상 고정하고 연 0.1~0.2%p만 개선 — OLED 믹스 개선과 중국 LCD 판가 압박이 상쇄된다고 봤다. 2021년(77.5%) 복귀는 Bull에서만 가정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>매출 실적</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>rev_actual</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>298780.43</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>261517.81</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>213308.19</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>266153.47</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>258100.82</v>
+      </c>
+      <c r="I18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>[객관] 요약연결재무정보.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>매출 성장률</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>rev_g</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="J19" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="K19" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L19" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N19" s="11" t="inlineStr">
+        <is>
+          <t>[주관] 2026년 −1% 후 연 +1%. 컨센서스 2026 EBITDA가 2025년과 사실상 같은 수준(48,059 vs 48,711억)이라 시장도 매출 성장을 보지 않는다. LCD 축소가 이어지고 OLED(Auto·IT)가 그 공백을 겨우 메우는 그림. 성장이 아니라 **수익성과 레버리지**가 이 종목의 이야기다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
           <t>순차입금</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>net_debt</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D20" s="9" t="n">
         <v>91222.09</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E20" s="9" t="n">
         <v>131667.61</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F20" s="9" t="n">
         <v>142716.07</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G20" s="9" t="n">
         <v>125284.74</v>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H20" s="9" t="n">
         <v>110920.8</v>
       </c>
-      <c r="I12" s="10" t="n">
+      <c r="I20" s="10" t="n">
         <v>110920.8</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J20" s="10" t="n">
         <v>110920.8</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K20" s="10" t="n">
         <v>110920.8</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L20" s="10" t="n">
         <v>110920.8</v>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M20" s="10" t="n">
         <v>110920.8</v>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N20" s="11" t="inlineStr">
         <is>
           <t>[객관 실적 / 추정 구간 고정] 단기차입금+유동성장기+장기차입금+사채 − 현금및현금성자산 (리스부채·파생 제외). 2022년 값이 두 보고서에서 14,991,410백만원으로 정확히 일치해 체인이 검증됐다. 정점 14.27조(2023)에서 11.09조(2025)로 2년간 3.2조 줄었다 — CAPEX 축소로 FCF가 돌기 시작한 결과다. 추정 구간은 2025년 수준 고정: 실제로는 더 줄 가능성이 높아 **보수적인 쪽**이지만, 차입 상환 속도를 모델링하려면 운전자본·리스·배당 가정이 다 필요해 넣지 않았다.</t>
         </is>
@@ -1429,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1597,43 +2015,43 @@
         </is>
       </c>
       <c r="D5" s="14">
-        <f>(D6-D20)</f>
+        <f>(D6-D31)</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>(E6-E20)</f>
+        <f>(E6-E31)</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>(F6-F20)</f>
+        <f>(F6-F31)</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>(G6-G20)</f>
+        <f>(G6-G31)</f>
         <v/>
       </c>
       <c r="H5" s="14">
-        <f>(H6-H20)</f>
+        <f>(H6-H31)</f>
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>(I6-I20)</f>
+        <f>(I6-I31)</f>
         <v/>
       </c>
       <c r="J5" s="14">
-        <f>(J6-J20)</f>
+        <f>(J6-J31)</f>
         <v/>
       </c>
       <c r="K5" s="14">
-        <f>(K6-K20)</f>
+        <f>(K6-K31)</f>
         <v/>
       </c>
       <c r="L5" s="14">
-        <f>(L6-L20)</f>
+        <f>(L6-L31)</f>
         <v/>
       </c>
       <c r="M5" s="14">
-        <f>(M6-M20)</f>
+        <f>(M6-M31)</f>
         <v/>
       </c>
     </row>
@@ -1758,43 +2176,43 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>(D9+D11)</f>
+        <f>(D9+D22)</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(E9+E11)</f>
+        <f>(E9+E22)</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(F9+F11)</f>
+        <f>(F9+F22)</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>(G9+G11)</f>
+        <f>(G9+G22)</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>(H9+H11)</f>
+        <f>(H9+H22)</f>
         <v/>
       </c>
       <c r="I8" s="17">
-        <f>(I9+I11)</f>
+        <f>(I9+I22)</f>
         <v/>
       </c>
       <c r="J8" s="17">
-        <f>(J9+J11)</f>
+        <f>(J9+J22)</f>
         <v/>
       </c>
       <c r="K8" s="17">
-        <f>(K9+K11)</f>
+        <f>(K9+K22)</f>
         <v/>
       </c>
       <c r="L8" s="17">
-        <f>(L9+L11)</f>
+        <f>(L9+L22)</f>
         <v/>
       </c>
       <c r="M8" s="17">
-        <f>(M9+M11)</f>
+        <f>(M9+M22)</f>
         <v/>
       </c>
     </row>
@@ -1815,55 +2233,55 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>(D17-D10)</f>
+        <f>(D28-D21)</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(E17-E10)</f>
+        <f>(E28-E21)</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(F17-F10)</f>
+        <f>(F28-F21)</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>(G17-G10)</f>
+        <f>(G28-G21)</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>(H17-H10)</f>
+        <f>(H28-H21)</f>
         <v/>
       </c>
       <c r="I9" s="17">
-        <f>(I17-I10)</f>
+        <f>(I28-I21)</f>
         <v/>
       </c>
       <c r="J9" s="17">
-        <f>(J17-J10)</f>
+        <f>(J28-J21)</f>
         <v/>
       </c>
       <c r="K9" s="17">
-        <f>(K17-K10)</f>
+        <f>(K28-K21)</f>
         <v/>
       </c>
       <c r="L9" s="17">
-        <f>(L17-L10)</f>
+        <f>(L28-L21)</f>
         <v/>
       </c>
       <c r="M9" s="17">
-        <f>(M17-M10)</f>
+        <f>(M28-M21)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>총비용</t>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
+          <t>net_income</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1872,543 +2290,1086 @@
         </is>
       </c>
       <c r="D10" s="16">
-        <f>(D11+D14)</f>
+        <f>IF((D11&gt;0),D12,(((D9+D13)*(1-D14))*D15))</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>(E11+E14)</f>
+        <f>IF((E11&gt;0),E12,(((E9+E13)*(1-E14))*E15))</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>(F11+F14)</f>
+        <f>IF((F11&gt;0),F12,(((F9+F13)*(1-F14))*F15))</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>(G11+G14)</f>
+        <f>IF((G11&gt;0),G12,(((G9+G13)*(1-G14))*G15))</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>(H11+H14)</f>
+        <f>IF((H11&gt;0),H12,(((H9+H13)*(1-H14))*H15))</f>
         <v/>
       </c>
       <c r="I10" s="17">
-        <f>(I11+I14)</f>
+        <f>IF((I11&gt;0),I12,(((I9+I13)*(1-I14))*I15))</f>
         <v/>
       </c>
       <c r="J10" s="17">
-        <f>(J11+J14)</f>
+        <f>IF((J11&gt;0),J12,(((J9+J13)*(1-J14))*J15))</f>
         <v/>
       </c>
       <c r="K10" s="17">
-        <f>(K11+K14)</f>
+        <f>IF((K11&gt;0),K12,(((K9+K13)*(1-K14))*K15))</f>
         <v/>
       </c>
       <c r="L10" s="17">
-        <f>(L11+L14)</f>
+        <f>IF((L11&gt;0),L12,(((L9+L13)*(1-L14))*L15))</f>
         <v/>
       </c>
       <c r="M10" s="17">
-        <f>(M11+M14)</f>
+        <f>IF((M11&gt;0),M12,(((M9+M13)*(1-M14))*M15))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>순이익 실적</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ni_actual</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D11" s="16">
-        <f>IF((D12&gt;0),D12,(0*(1+D13)))</f>
-        <v/>
-      </c>
-      <c r="E11" s="16">
-        <f>IF((E12&gt;0),E12,(D11*(1+E13)))</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
-        <f>IF((F12&gt;0),F12,(E11*(1+F13)))</f>
-        <v/>
-      </c>
-      <c r="G11" s="16">
-        <f>IF((G12&gt;0),G12,(F11*(1+G13)))</f>
-        <v/>
-      </c>
-      <c r="H11" s="16">
-        <f>IF((H12&gt;0),H12,(G11*(1+H13)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>IF((I12&gt;0),I12,(H11*(1+I13)))</f>
-        <v/>
-      </c>
-      <c r="J11" s="17">
-        <f>IF((J12&gt;0),J12,(I11*(1+J13)))</f>
-        <v/>
-      </c>
-      <c r="K11" s="17">
-        <f>IF((K12&gt;0),K12,(J11*(1+K13)))</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
-        <f>IF((L12&gt;0),L12,(K11*(1+L13)))</f>
-        <v/>
-      </c>
-      <c r="M11" s="17">
-        <f>IF((M12&gt;0),M12,(L11*(1+M13)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>감가상각 실적</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>dep_actual</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="D12" s="19" t="n">
+        <v>11861.82</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-30715.65</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-27337.42</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>-25626.06</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>2263.12</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>영업외손익</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>nonop</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D12" s="19" t="n">
-        <v>45007.01</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>45574.57</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>42137.42</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>51256.37</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>43541.45</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="24" t="inlineStr">
-        <is>
-          <t>감가상각 증가율</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>dep_g</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="26" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L13" s="26" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>-0.03</v>
+      <c r="D13" s="19" t="n">
+        <v>-5117.23</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-13483.23</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-8292.77</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>-16309.44</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-152.88</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>-300</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>-300</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>-300</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>-300</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>-300</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="23" t="inlineStr">
         <is>
+          <t>실효세율</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L14" s="25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M14" s="25" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>지배지분 비율</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ctrl_ratio</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L15" s="25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>EPS (참고)</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D16" s="16">
+        <f>((D10/D17)*100)</f>
+        <v/>
+      </c>
+      <c r="E16" s="16">
+        <f>((E10/E17)*100)</f>
+        <v/>
+      </c>
+      <c r="F16" s="16">
+        <f>((F10/F17)*100)</f>
+        <v/>
+      </c>
+      <c r="G16" s="16">
+        <f>((G10/G17)*100)</f>
+        <v/>
+      </c>
+      <c r="H16" s="16">
+        <f>((H10/H17)*100)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17">
+        <f>((I10/I17)*100)</f>
+        <v/>
+      </c>
+      <c r="J16" s="17">
+        <f>((J10/J17)*100)</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>((K10/K17)*100)</f>
+        <v/>
+      </c>
+      <c r="L16" s="17">
+        <f>((L10/L17)*100)</f>
+        <v/>
+      </c>
+      <c r="M16" s="17">
+        <f>((M10/M17)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>상장주식수</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>백만주</t>
+        </is>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>500</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>500</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>DPS (참고)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D18" s="16">
+        <f>IF((D11&gt;0),D19,(D16*D20))</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>IF((E11&gt;0),E19,(E16*E20))</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>IF((F11&gt;0),F19,(F16*F20))</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>IF((G11&gt;0),G19,(G16*G20))</f>
+        <v/>
+      </c>
+      <c r="H18" s="16">
+        <f>IF((H11&gt;0),H19,(H16*H20))</f>
+        <v/>
+      </c>
+      <c r="I18" s="17">
+        <f>IF((I11&gt;0),I19,(I16*I20))</f>
+        <v/>
+      </c>
+      <c r="J18" s="17">
+        <f>IF((J11&gt;0),J19,(J16*J20))</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>IF((K11&gt;0),K19,(K16*K20))</f>
+        <v/>
+      </c>
+      <c r="L18" s="17">
+        <f>IF((L11&gt;0),L19,(L16*L20))</f>
+        <v/>
+      </c>
+      <c r="M18" s="17">
+        <f>IF((M11&gt;0),M19,(M16*M20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>DPS 실적</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>dps_a</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>650</v>
+      </c>
+      <c r="E19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>총비용</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>total_cost</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D21" s="16">
+        <f>(D22+D25)</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>(E22+E25)</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>(F22+F25)</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>(G22+G25)</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>(H22+H25)</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>(I22+I25)</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>(J22+J25)</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>(K22+K25)</f>
+        <v/>
+      </c>
+      <c r="L21" s="17">
+        <f>(L22+L25)</f>
+        <v/>
+      </c>
+      <c r="M21" s="17">
+        <f>(M22+M25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D22" s="16">
+        <f>IF((D23&gt;0),D23,(0*(1+D24)))</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>IF((E23&gt;0),E23,(D22*(1+E24)))</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>IF((F23&gt;0),F23,(E22*(1+F24)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>IF((G23&gt;0),G23,(F22*(1+G24)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>IF((H23&gt;0),H23,(G22*(1+H24)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>IF((I23&gt;0),I23,(H22*(1+I24)))</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>IF((J23&gt;0),J23,(I22*(1+J24)))</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>IF((K23&gt;0),K23,(J22*(1+K24)))</f>
+        <v/>
+      </c>
+      <c r="L22" s="17">
+        <f>IF((L23&gt;0),L23,(K22*(1+L24)))</f>
+        <v/>
+      </c>
+      <c r="M22" s="17">
+        <f>IF((M23&gt;0),M23,(L22*(1+M24)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26" t="inlineStr">
+        <is>
+          <t>감가상각 실적</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+      <c r="D23" s="19" t="n">
+        <v>45007.01</v>
+      </c>
+      <c r="E23" s="19" t="n">
+        <v>45574.57</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>42137.42</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>51256.37</v>
+      </c>
+      <c r="H23" s="19" t="n">
+        <v>43541.45</v>
+      </c>
+      <c r="I23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="25" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="J24" s="25" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="K24" s="25" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L24" s="25" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M24" s="25" t="n">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
           <t>기타비용</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>other_cost</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D14" s="16">
-        <f>IF((D15&gt;0),D15,(D17*D16))</f>
-        <v/>
-      </c>
-      <c r="E14" s="16">
-        <f>IF((E15&gt;0),E15,(E17*E16))</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
-        <f>IF((F15&gt;0),F15,(F17*F16))</f>
-        <v/>
-      </c>
-      <c r="G14" s="16">
-        <f>IF((G15&gt;0),G15,(G17*G16))</f>
-        <v/>
-      </c>
-      <c r="H14" s="16">
-        <f>IF((H15&gt;0),H15,(H17*H16))</f>
-        <v/>
-      </c>
-      <c r="I14" s="17">
-        <f>IF((I15&gt;0),I15,(I17*I16))</f>
-        <v/>
-      </c>
-      <c r="J14" s="17">
-        <f>IF((J15&gt;0),J15,(J17*J16))</f>
-        <v/>
-      </c>
-      <c r="K14" s="17">
-        <f>IF((K15&gt;0),K15,(K17*K16))</f>
-        <v/>
-      </c>
-      <c r="L14" s="17">
-        <f>IF((L15&gt;0),L15,(L17*L16))</f>
-        <v/>
-      </c>
-      <c r="M14" s="17">
-        <f>IF((M15&gt;0),M15,(M17*M16))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="D25" s="16">
+        <f>IF((D26&gt;0),D26,(D28*D27))</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>IF((E26&gt;0),E26,(E28*E27))</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>IF((F26&gt;0),F26,(F28*F27))</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>IF((G26&gt;0),G26,(G28*G27))</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IF((H26&gt;0),H26,(H28*H27))</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>IF((I26&gt;0),I26,(I28*I27))</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>IF((J26&gt;0),J26,(J28*J27))</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>IF((K26&gt;0),K26,(K28*K27))</f>
+        <v/>
+      </c>
+      <c r="L25" s="17">
+        <f>IF((L26&gt;0),L26,(L28*L27))</f>
+        <v/>
+      </c>
+      <c r="M25" s="17">
+        <f>IF((M26&gt;0),M26,(M28*M27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>기타비용 실적</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>other_actual</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D26" s="19" t="n">
         <v>231467.34</v>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E26" s="19" t="n">
         <v>236793.71</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F26" s="19" t="n">
         <v>196272.41</v>
       </c>
-      <c r="G15" s="19" t="n">
+      <c r="G26" s="19" t="n">
         <v>220503.06</v>
       </c>
-      <c r="H15" s="19" t="n">
+      <c r="H26" s="19" t="n">
         <v>209389.6</v>
       </c>
-      <c r="I15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="I26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>기타비용률</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>other_ratio</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="26" t="n">
+      <c r="D27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="25" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="J16" s="26" t="n">
+      <c r="J27" s="25" t="n">
         <v>0.8080000000000001</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K27" s="25" t="n">
         <v>0.806</v>
       </c>
-      <c r="L16" s="26" t="n">
+      <c r="L27" s="25" t="n">
         <v>0.805</v>
       </c>
-      <c r="M16" s="26" t="n">
+      <c r="M27" s="25" t="n">
         <v>0.804</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="22" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D17" s="16">
-        <f>IF((D18&gt;0),D18,(0*(1+D19)))</f>
-        <v/>
-      </c>
-      <c r="E17" s="16">
-        <f>IF((E18&gt;0),E18,(D17*(1+E19)))</f>
-        <v/>
-      </c>
-      <c r="F17" s="16">
-        <f>IF((F18&gt;0),F18,(E17*(1+F19)))</f>
-        <v/>
-      </c>
-      <c r="G17" s="16">
-        <f>IF((G18&gt;0),G18,(F17*(1+G19)))</f>
-        <v/>
-      </c>
-      <c r="H17" s="16">
-        <f>IF((H18&gt;0),H18,(G17*(1+H19)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="17">
-        <f>IF((I18&gt;0),I18,(H17*(1+I19)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="17">
-        <f>IF((J18&gt;0),J18,(I17*(1+J19)))</f>
-        <v/>
-      </c>
-      <c r="K17" s="17">
-        <f>IF((K18&gt;0),K18,(J17*(1+K19)))</f>
-        <v/>
-      </c>
-      <c r="L17" s="17">
-        <f>IF((L18&gt;0),L18,(K17*(1+L19)))</f>
-        <v/>
-      </c>
-      <c r="M17" s="17">
-        <f>IF((M18&gt;0),M18,(L17*(1+M19)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="D28" s="16">
+        <f>IF((D29&gt;0),D29,(0*(1+D30)))</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>IF((E29&gt;0),E29,(D28*(1+E30)))</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>IF((F29&gt;0),F29,(E28*(1+F30)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>IF((G29&gt;0),G29,(F28*(1+G30)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>IF((H29&gt;0),H29,(G28*(1+H30)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>IF((I29&gt;0),I29,(H28*(1+I30)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>IF((J29&gt;0),J29,(I28*(1+J30)))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF((K29&gt;0),K29,(J28*(1+K30)))</f>
+        <v/>
+      </c>
+      <c r="L28" s="17">
+        <f>IF((L29&gt;0),L29,(K28*(1+L30)))</f>
+        <v/>
+      </c>
+      <c r="M28" s="17">
+        <f>IF((M29&gt;0),M29,(L28*(1+M30)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>매출 실적</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>rev_actual</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D29" s="19" t="n">
         <v>298780.43</v>
       </c>
-      <c r="E18" s="19" t="n">
+      <c r="E29" s="19" t="n">
         <v>261517.81</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F29" s="19" t="n">
         <v>213308.19</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G29" s="19" t="n">
         <v>266153.47</v>
       </c>
-      <c r="H18" s="19" t="n">
+      <c r="H29" s="19" t="n">
         <v>258100.82</v>
       </c>
-      <c r="I18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="I29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>매출 성장률</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>rev_g</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="26" t="n">
+      <c r="D30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="25" t="n">
         <v>-0.01</v>
       </c>
-      <c r="J19" s="26" t="n">
+      <c r="J30" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K30" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="L30" s="25" t="n">
         <v>0.01</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="M30" s="25" t="n">
         <v>0.01</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>순차입금</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>net_debt</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D31" s="19" t="n">
         <v>91222.09</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E31" s="19" t="n">
         <v>131667.61</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F31" s="19" t="n">
         <v>142716.07</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G31" s="19" t="n">
         <v>125284.74</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H31" s="19" t="n">
         <v>110920.8</v>
       </c>
-      <c r="I20" s="20" t="n">
+      <c r="I31" s="20" t="n">
         <v>110920.8</v>
       </c>
-      <c r="J20" s="20" t="n">
+      <c r="J31" s="20" t="n">
         <v>110920.8</v>
       </c>
-      <c r="K20" s="20" t="n">
+      <c r="K31" s="20" t="n">
         <v>110920.8</v>
       </c>
-      <c r="L20" s="20" t="n">
+      <c r="L31" s="20" t="n">
         <v>110920.8</v>
       </c>
-      <c r="M20" s="20" t="n">
+      <c r="M31" s="20" t="n">
         <v>110920.8</v>
       </c>
     </row>
@@ -2423,7 +3384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2488,14 +3449,14 @@
       <c r="C5" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>ev_value - net_debt</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>'=(I6-I20)</t>
+          <t>'=(I6-I31)</t>
         </is>
       </c>
     </row>
@@ -2513,7 +3474,7 @@
       <c r="C6" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="28" t="inlineStr">
         <is>
           <t>ebitda * target_ev_ebitda</t>
         </is>
@@ -2538,14 +3499,14 @@
       <c r="C7" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="28" t="inlineStr">
         <is>
           <t>op_profit + dep_total</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>'=(I9+I11)</t>
+          <t>'=(I9+I22)</t>
         </is>
       </c>
     </row>
@@ -2563,114 +3524,189 @@
       <c r="C8" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D8" s="27" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>revenue - total_cost</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>'=(I17-I10)</t>
+          <t>'=(I28-I21)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
+          <t>net_income</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>총비용</t>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>dep_total + other_cost</t>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>IF(ni_hist &gt; 0, ni_actual, (op_profit + nonop) * (1 - tax_rate) * ctrl_ratio)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>'=(I11+I14)</t>
+          <t>'=IF((I11&gt;0),I12,(((I9+I13)*(1-I14))*I15))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>감가상각비</t>
+          <t>EPS (참고)</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>IF(dep_actual &gt; 0, dep_actual, PREV(dep_total) * (1 + dep_g))</t>
+        <v>16</v>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>net_income / shares * 100</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>'=IF((I12&gt;0),I12,(H11*(1+I13)))</t>
+          <t>'=((I10/I17)*100)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>other_cost</t>
+          <t>dps</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>기타비용</t>
+          <t>DPS (참고)</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>IF(other_actual &gt; 0, other_actual, revenue * other_ratio)</t>
+        <v>18</v>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>IF(ni_hist &gt; 0, dps_a, eps * payout)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>'=IF((I15&gt;0),I15,(I17*I16))</t>
+          <t>'=IF((I11&gt;0),I19,(I16*I20))</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>total_cost</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>총비용</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>dep_total + other_cost</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>'=(I22+I25)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>IF(dep_actual &gt; 0, dep_actual, PREV(dep_total) * (1 + dep_g))</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>'=IF((I23&gt;0),I23,(H22*(1+I24)))</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>other_cost</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="28" t="inlineStr">
+        <is>
+          <t>IF(other_actual &gt; 0, other_actual, revenue * other_ratio)</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>'=IF((I26&gt;0),I26,(I28*I27))</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="C15" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>IF(rev_actual &gt; 0, rev_actual, PREV(revenue) * (1 + rev_g))</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>'=IF((I18&gt;0),I18,(H17*(1+I19)))</t>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>'=IF((I29&gt;0),I29,(H28*(1+I30)))</t>
         </is>
       </c>
     </row>
@@ -2685,7 +3721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2776,7 +3812,7 @@
           <t>ev_value</t>
         </is>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>사업가치 (EV)</t>
         </is>
@@ -2805,7 +3841,7 @@
           <t>target_ev_ebitda</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>목표 EV/EBITDA</t>
         </is>
@@ -2834,7 +3870,7 @@
           <t>ebitda</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
@@ -2863,7 +3899,7 @@
           <t>op_profit</t>
         </is>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
@@ -2889,12 +3925,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>total_cost</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>총비용</t>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>지배주주 순이익 (참고)</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2905,11 +3941,7 @@
           <t>computed</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>10</v>
       </c>
@@ -2922,12 +3954,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>dep_total</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
+          <t>ni_hist</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>순이익 실적 마스크</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2935,32 +3967,28 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
         <v>11</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>억원</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>dep_actual</t>
+          <t>ni_actual</t>
         </is>
       </c>
       <c r="B11" s="33" t="inlineStr">
         <is>
-          <t>감가상각 실적</t>
+          <t>순이익 실적</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2980,16 +4008,16 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>dep_g</t>
+          <t>nonop</t>
         </is>
       </c>
       <c r="B12" s="33" t="inlineStr">
         <is>
-          <t>감가상각 증가율</t>
+          <t>영업외손익</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3002,19 +4030,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>억원</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>other_cost</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>기타비용</t>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="B13" s="33" t="inlineStr">
+        <is>
+          <t>실효세율</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3022,7 +4050,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -3031,23 +4059,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>other_actual</t>
+          <t>ctrl_ratio</t>
         </is>
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>기타비용 실적</t>
+          <t>지배지분 비율</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3060,27 +4088,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>other_ratio</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="B15" s="33" t="inlineStr">
         <is>
-          <t>기타비용률</t>
+          <t>EPS (참고)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -3089,27 +4117,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>revenue</t>
-        </is>
-      </c>
-      <c r="B16" s="31" t="inlineStr">
-        <is>
-          <t>매출</t>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>상장주식수</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>computed</t>
+          <t>input</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -3118,27 +4146,27 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>백만주</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>rev_actual</t>
-        </is>
-      </c>
-      <c r="B17" s="32" t="inlineStr">
-        <is>
-          <t>매출 실적</t>
+          <t>dps</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>DPS (참고)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -3147,23 +4175,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>억원</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>rev_g</t>
-        </is>
-      </c>
-      <c r="B18" s="32" t="inlineStr">
-        <is>
-          <t>매출 성장률</t>
+          <t>dps_a</t>
+        </is>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>DPS 실적</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3176,23 +4204,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>원</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>net_debt</t>
-        </is>
-      </c>
-      <c r="B19" s="28" t="inlineStr">
-        <is>
-          <t>순차입금</t>
+          <t>payout</t>
+        </is>
+      </c>
+      <c r="B19" s="35" t="inlineStr">
+        <is>
+          <t>배당성향</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3204,6 +4232,329 @@
         <v>20</v>
       </c>
       <c r="G19" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>total_cost</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>총비용</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>21</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>dep_total</t>
+        </is>
+      </c>
+      <c r="B21" s="33" t="inlineStr">
+        <is>
+          <t>감가상각비</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>22</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>dep_actual</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>감가상각 실적</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>23</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>dep_g</t>
+        </is>
+      </c>
+      <c r="B23" s="34" t="inlineStr">
+        <is>
+          <t>감가상각 증가율</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>24</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>other_cost</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>기타비용</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>other_actual</t>
+        </is>
+      </c>
+      <c r="B25" s="34" t="inlineStr">
+        <is>
+          <t>기타비용 실적</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>26</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>other_ratio</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>기타비용률</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>computed</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>rev_actual</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>매출 실적</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>29</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>억원</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>rev_g</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>매출 성장률</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>net_debt</t>
+        </is>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>순차입금</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>31</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>억원</t>
         </is>
@@ -3376,44 +4727,44 @@
           <t>부모 − 자식합</t>
         </is>
       </c>
-      <c r="D5" s="34">
-        <f>ROUND(Model!D10-(Model!D11+Model!D14),6)</f>
-        <v/>
-      </c>
-      <c r="E5" s="34">
-        <f>ROUND(Model!E10-(Model!E11+Model!E14),6)</f>
-        <v/>
-      </c>
-      <c r="F5" s="34">
-        <f>ROUND(Model!F10-(Model!F11+Model!F14),6)</f>
-        <v/>
-      </c>
-      <c r="G5" s="34">
-        <f>ROUND(Model!G10-(Model!G11+Model!G14),6)</f>
-        <v/>
-      </c>
-      <c r="H5" s="34">
-        <f>ROUND(Model!H10-(Model!H11+Model!H14),6)</f>
-        <v/>
-      </c>
-      <c r="I5" s="34">
-        <f>ROUND(Model!I10-(Model!I11+Model!I14),6)</f>
-        <v/>
-      </c>
-      <c r="J5" s="34">
-        <f>ROUND(Model!J10-(Model!J11+Model!J14),6)</f>
-        <v/>
-      </c>
-      <c r="K5" s="34">
-        <f>ROUND(Model!K10-(Model!K11+Model!K14),6)</f>
-        <v/>
-      </c>
-      <c r="L5" s="34">
-        <f>ROUND(Model!L10-(Model!L11+Model!L14),6)</f>
-        <v/>
-      </c>
-      <c r="M5" s="34">
-        <f>ROUND(Model!M10-(Model!M11+Model!M14),6)</f>
+      <c r="D5" s="36">
+        <f>ROUND(Model!D21-(Model!D22+Model!D25),6)</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>ROUND(Model!E21-(Model!E22+Model!E25),6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="36">
+        <f>ROUND(Model!F21-(Model!F22+Model!F25),6)</f>
+        <v/>
+      </c>
+      <c r="G5" s="36">
+        <f>ROUND(Model!G21-(Model!G22+Model!G25),6)</f>
+        <v/>
+      </c>
+      <c r="H5" s="36">
+        <f>ROUND(Model!H21-(Model!H22+Model!H25),6)</f>
+        <v/>
+      </c>
+      <c r="I5" s="36">
+        <f>ROUND(Model!I21-(Model!I22+Model!I25),6)</f>
+        <v/>
+      </c>
+      <c r="J5" s="36">
+        <f>ROUND(Model!J21-(Model!J22+Model!J25),6)</f>
+        <v/>
+      </c>
+      <c r="K5" s="36">
+        <f>ROUND(Model!K21-(Model!K22+Model!K25),6)</f>
+        <v/>
+      </c>
+      <c r="L5" s="36">
+        <f>ROUND(Model!L21-(Model!L22+Model!L25),6)</f>
+        <v/>
+      </c>
+      <c r="M5" s="36">
+        <f>ROUND(Model!M21-(Model!M22+Model!M25),6)</f>
         <v/>
       </c>
     </row>
@@ -3472,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a046450d1b60700b</t>
+          <t>e73d0be6051e5726</t>
         </is>
       </c>
     </row>
@@ -3507,7 +4858,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -3517,7 +4868,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>e73d0be6051e5726</t>
+          <t>c909803cfe2212bf</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c909803cfe2212bf</t>
+          <t>911d7c903749a2a9</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>911d7c903749a2a9</t>
+          <t>ee2d24a48f0ff248</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ee2d24a48f0ff248</t>
+          <t>c951b892c8a22221</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c951b892c8a22221</t>
+          <t>69575d83920772d4</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>69575d83920772d4</t>
+          <t>d3f520bca14dc88a</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>d3f520bca14dc88a</t>
+          <t>6fe4efbf0e03f75b</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6fe4efbf0e03f75b</t>
+          <t>b41547f80f210292</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>b41547f80f210292</t>
+          <t>09d38fd4efe66d19</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09d38fd4efe66d19</t>
+          <t>34ae96bc620f3495</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>34ae96bc620f3495</t>
+          <t>7268c751d0554c2b</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7268c751d0554c2b</t>
+          <t>5fdc4b1627766374</t>
         </is>
       </c>
     </row>
